--- a/tests/fixtures/manual_test.xlsx
+++ b/tests/fixtures/manual_test.xlsx
@@ -581,7 +581,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>大量データ 80行目</t>
+          <t>大量データ 50行目</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>大量データ 130行目</t>
+          <t>大量データ 80行目</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>80行目へ</t>
+          <t>50行目へ</t>
         </is>
       </c>
     </row>
@@ -1361,404 +1361,454 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>S029</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>29000</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>S030</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D32" s="17" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>S031</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>31000</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>2</v>
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>【テーブル2】在庫データ</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>S032</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>32000</v>
-      </c>
-      <c r="D34" s="17" t="n">
-        <v>3</v>
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>在庫ID</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>倉庫</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>在庫数</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>リンク</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>S033</t>
+          <t>Z001</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>大阪</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
           <t>商品B</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>33000</v>
-      </c>
       <c r="D35" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>S034</t>
+          <t>Z002</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
+          <t>名古屋</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
           <t>商品C</t>
         </is>
       </c>
-      <c r="C36" s="17" t="n">
-        <v>34000</v>
-      </c>
       <c r="D36" s="17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>S035</t>
+          <t>Z003</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
+          <t>福岡</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
           <t>商品D</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>35000</v>
-      </c>
       <c r="D37" s="5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>S036</t>
+          <t>Z004</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
+          <t>東京</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
           <t>商品A</t>
         </is>
       </c>
-      <c r="C38" s="17" t="n">
-        <v>36000</v>
-      </c>
       <c r="D38" s="17" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>S037</t>
+          <t>Z005</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
+          <t>大阪</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
           <t>商品B</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>37000</v>
-      </c>
       <c r="D39" s="5" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>S038</t>
+          <t>Z006</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
+          <t>名古屋</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
           <t>商品C</t>
         </is>
       </c>
-      <c r="C40" s="17" t="n">
-        <v>38000</v>
-      </c>
       <c r="D40" s="17" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>S039</t>
+          <t>Z007</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>福岡</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
           <t>商品D</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>39000</v>
-      </c>
       <c r="D41" s="5" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>S040</t>
+          <t>Z008</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
+          <t>東京</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
           <t>商品A</t>
         </is>
       </c>
-      <c r="C42" s="17" t="n">
-        <v>40000</v>
-      </c>
       <c r="D42" s="17" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>S041</t>
+          <t>Z009</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>大阪</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
           <t>商品B</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>41000</v>
-      </c>
       <c r="D43" s="5" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>S042</t>
+          <t>Z010</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
+          <t>名古屋</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
           <t>商品C</t>
         </is>
       </c>
-      <c r="C44" s="17" t="n">
-        <v>42000</v>
-      </c>
       <c r="D44" s="17" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>S043</t>
+          <t>Z011</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
+          <t>福岡</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
           <t>商品D</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>43000</v>
-      </c>
       <c r="D45" s="5" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>S044</t>
+          <t>Z012</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
+          <t>東京</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
           <t>商品A</t>
         </is>
       </c>
-      <c r="C46" s="17" t="n">
-        <v>44000</v>
-      </c>
       <c r="D46" s="17" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>S045</t>
+          <t>Z013</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
+          <t>大阪</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
           <t>商品B</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>45000</v>
-      </c>
       <c r="D47" s="5" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>S046</t>
+          <t>Z014</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
+          <t>名古屋</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
           <t>商品C</t>
         </is>
       </c>
-      <c r="C48" s="17" t="n">
-        <v>46000</v>
-      </c>
       <c r="D48" s="17" t="n">
-        <v>7</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>S047</t>
+          <t>Z015</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>福岡</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
           <t>商品D</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
-        <v>47000</v>
-      </c>
       <c r="D49" s="5" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>S048</t>
+          <t>Z016</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
+          <t>東京</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
           <t>商品A</t>
         </is>
       </c>
-      <c r="C50" s="17" t="n">
-        <v>48000</v>
-      </c>
       <c r="D50" s="17" t="n">
-        <v>9</v>
+        <v>160</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>10行目へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Z017</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>大阪</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>商品B</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>80行目へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Z018</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>名古屋</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>商品C</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>【テーブル2】在庫データ</t>
-        </is>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Z019</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>福岡</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>商品D</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>在庫ID</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>倉庫</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>在庫数</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>リンク</t>
-        </is>
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Z020</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>東京</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>商品A</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Z001</t>
+          <t>Z021</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -1772,13 +1822,13 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>10</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>Z002</t>
+          <t>Z022</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -1792,13 +1842,13 @@
         </is>
       </c>
       <c r="D56" s="17" t="n">
-        <v>20</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Z003</t>
+          <t>Z023</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -1812,13 +1862,13 @@
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>30</v>
+        <v>230</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>Z004</t>
+          <t>Z024</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -1832,13 +1882,13 @@
         </is>
       </c>
       <c r="D58" s="17" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Z005</t>
+          <t>Z025</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1852,13 +1902,13 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>Z006</t>
+          <t>Z026</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -1872,13 +1922,13 @@
         </is>
       </c>
       <c r="D60" s="17" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Z007</t>
+          <t>Z027</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1892,13 +1942,13 @@
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>Z008</t>
+          <t>Z028</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -1912,1909 +1962,659 @@
         </is>
       </c>
       <c r="D62" s="17" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Z009</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>大阪</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>Z010</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>名古屋</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Z011</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>福岡</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>110</v>
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>【テーブル3】顧客データ</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="inlineStr">
-        <is>
-          <t>Z012</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="n">
-        <v>120</v>
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>顧客ID</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>地域</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>会員ランク</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>リンク</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Z013</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>顧客001</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>130</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>シルバー</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>Z014</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>名古屋</t>
+          <t>顧客002</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="n">
-        <v>140</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>ブロンズ</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Z015</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>福岡</t>
+          <t>顧客003</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="n">
-        <v>150</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>Z016</t>
+          <t>C004</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>顧客004</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D70" s="17" t="n">
-        <v>160</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>ゴールド</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Z017</t>
+          <t>C005</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>顧客005</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>170</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>シルバー</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>Z018</t>
+          <t>C006</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>名古屋</t>
+          <t>顧客006</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="n">
-        <v>180</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>ブロンズ</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Z019</t>
+          <t>C007</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>福岡</t>
+          <t>顧客007</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="n">
-        <v>190</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>Z020</t>
+          <t>C008</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>顧客008</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="n">
-        <v>200</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>ゴールド</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Z021</t>
+          <t>C009</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>顧客009</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>210</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>シルバー</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>Z022</t>
+          <t>C010</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>名古屋</t>
+          <t>顧客010</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="n">
-        <v>220</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>ブロンズ</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Z023</t>
+          <t>C011</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>福岡</t>
+          <t>顧客011</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>230</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="17" t="inlineStr">
         <is>
-          <t>Z024</t>
+          <t>C012</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>顧客012</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="n">
-        <v>240</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>ゴールド</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Z025</t>
+          <t>C013</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>顧客013</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="n">
-        <v>250</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>シルバー</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>Z026</t>
+          <t>C014</t>
         </is>
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>名古屋</t>
+          <t>顧客014</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="n">
-        <v>260</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>ブロンズ</t>
+        </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>10行目へ</t>
+          <t>目次へ戻る</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Z027</t>
+          <t>C015</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>福岡</t>
+          <t>顧客015</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>270</v>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>130行目へ</t>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>一般</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>Z028</t>
+          <t>C016</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>顧客016</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="n">
-        <v>280</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>ゴールド</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Z029</t>
+          <t>C017</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>顧客017</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="n">
-        <v>290</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>シルバー</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>Z030</t>
+          <t>C018</t>
         </is>
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>名古屋</t>
+          <t>顧客018</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D84" s="17" t="n">
-        <v>300</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>ブロンズ</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Z031</t>
+          <t>C019</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>福岡</t>
+          <t>顧客019</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="n">
-        <v>310</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>Z032</t>
+          <t>C020</t>
         </is>
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>顧客020</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D86" s="17" t="n">
-        <v>320</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>ゴールド</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Z033</t>
+          <t>C021</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>顧客021</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="n">
-        <v>330</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>シルバー</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>Z034</t>
+          <t>C022</t>
         </is>
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>名古屋</t>
+          <t>顧客022</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D88" s="17" t="n">
-        <v>340</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>ブロンズ</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Z035</t>
+          <t>C023</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>福岡</t>
+          <t>顧客023</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>350</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>Z036</t>
+          <t>C024</t>
         </is>
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>顧客024</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D90" s="17" t="n">
-        <v>360</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>ゴールド</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Z037</t>
+          <t>C025</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>大阪</t>
+          <t>顧客025</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="n">
-        <v>370</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>シルバー</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t>Z038</t>
+          <t>C026</t>
         </is>
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>名古屋</t>
+          <t>顧客026</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D92" s="17" t="n">
-        <v>380</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>ブロンズ</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Z039</t>
+          <t>C027</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>福岡</t>
+          <t>顧客027</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>390</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>Z040</t>
+          <t>C028</t>
         </is>
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>顧客028</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D94" s="17" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Z041</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>大阪</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="17" t="inlineStr">
-        <is>
-          <t>Z042</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>名古屋</t>
-        </is>
-      </c>
-      <c r="C96" s="17" t="inlineStr">
-        <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D96" s="17" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Z043</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>福岡</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="17" t="inlineStr">
-        <is>
-          <t>Z044</t>
-        </is>
-      </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="inlineStr">
-        <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D98" s="17" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Z045</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>大阪</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>商品B</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="17" t="inlineStr">
-        <is>
-          <t>Z046</t>
-        </is>
-      </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>名古屋</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
-        <is>
-          <t>商品C</t>
-        </is>
-      </c>
-      <c r="D100" s="17" t="n">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Z047</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>福岡</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>商品D</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="17" t="inlineStr">
-        <is>
-          <t>Z048</t>
-        </is>
-      </c>
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
-        <is>
-          <t>商品A</t>
-        </is>
-      </c>
-      <c r="D102" s="17" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="15" t="inlineStr">
-        <is>
-          <t>【テーブル3】顧客データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="19" t="inlineStr">
-        <is>
-          <t>顧客ID</t>
-        </is>
-      </c>
-      <c r="B106" s="19" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
-      <c r="C106" s="19" t="inlineStr">
-        <is>
-          <t>地域</t>
-        </is>
-      </c>
-      <c r="D106" s="19" t="inlineStr">
-        <is>
-          <t>会員ランク</t>
-        </is>
-      </c>
-      <c r="E106" s="19" t="inlineStr">
-        <is>
-          <t>リンク</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>顧客001</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="17" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B108" s="17" t="inlineStr">
-        <is>
-          <t>顧客002</t>
-        </is>
-      </c>
-      <c r="C108" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D108" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>顧客003</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="17" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="B110" s="17" t="inlineStr">
-        <is>
-          <t>顧客004</t>
-        </is>
-      </c>
-      <c r="C110" s="17" t="inlineStr">
-        <is>
           <t>関東</t>
         </is>
       </c>
-      <c r="D110" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>C005</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>顧客005</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="17" t="inlineStr">
-        <is>
-          <t>C006</t>
-        </is>
-      </c>
-      <c r="B112" s="17" t="inlineStr">
-        <is>
-          <t>顧客006</t>
-        </is>
-      </c>
-      <c r="C112" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D112" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>C007</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>顧客007</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t>C008</t>
-        </is>
-      </c>
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>顧客008</t>
-        </is>
-      </c>
-      <c r="C114" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D114" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>C009</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>顧客009</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="17" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="B116" s="17" t="inlineStr">
-        <is>
-          <t>顧客010</t>
-        </is>
-      </c>
-      <c r="C116" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D116" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>C011</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>顧客011</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="17" t="inlineStr">
-        <is>
-          <t>C012</t>
-        </is>
-      </c>
-      <c r="B118" s="17" t="inlineStr">
-        <is>
-          <t>顧客012</t>
-        </is>
-      </c>
-      <c r="C118" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D118" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>C013</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>顧客013</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="17" t="inlineStr">
-        <is>
-          <t>C014</t>
-        </is>
-      </c>
-      <c r="B120" s="17" t="inlineStr">
-        <is>
-          <t>顧客014</t>
-        </is>
-      </c>
-      <c r="C120" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D120" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>C015</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>顧客015</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="17" t="inlineStr">
-        <is>
-          <t>C016</t>
-        </is>
-      </c>
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t>顧客016</t>
-        </is>
-      </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D122" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>C017</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>顧客017</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="17" t="inlineStr">
-        <is>
-          <t>C018</t>
-        </is>
-      </c>
-      <c r="B124" s="17" t="inlineStr">
-        <is>
-          <t>顧客018</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D124" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>C019</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>顧客019</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="17" t="inlineStr">
-        <is>
-          <t>C020</t>
-        </is>
-      </c>
-      <c r="B126" s="17" t="inlineStr">
-        <is>
-          <t>顧客020</t>
-        </is>
-      </c>
-      <c r="C126" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D126" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>C021</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>顧客021</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="17" t="inlineStr">
-        <is>
-          <t>C022</t>
-        </is>
-      </c>
-      <c r="B128" s="17" t="inlineStr">
-        <is>
-          <t>顧客022</t>
-        </is>
-      </c>
-      <c r="C128" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D128" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>C023</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>顧客023</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="17" t="inlineStr">
-        <is>
-          <t>C024</t>
-        </is>
-      </c>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>顧客024</t>
-        </is>
-      </c>
-      <c r="C130" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D130" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>目次へ戻る</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>C025</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>顧客025</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="17" t="inlineStr">
-        <is>
-          <t>C026</t>
-        </is>
-      </c>
-      <c r="B132" s="17" t="inlineStr">
-        <is>
-          <t>顧客026</t>
-        </is>
-      </c>
-      <c r="C132" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D132" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>C027</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>顧客027</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
-          <t>C028</t>
-        </is>
-      </c>
-      <c r="B134" s="17" t="inlineStr">
-        <is>
-          <t>顧客028</t>
-        </is>
-      </c>
-      <c r="C134" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D134" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>C029</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>顧客029</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="17" t="inlineStr">
-        <is>
-          <t>C030</t>
-        </is>
-      </c>
-      <c r="B136" s="17" t="inlineStr">
-        <is>
-          <t>顧客030</t>
-        </is>
-      </c>
-      <c r="C136" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D136" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>C031</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>顧客031</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="17" t="inlineStr">
-        <is>
-          <t>C032</t>
-        </is>
-      </c>
-      <c r="B138" s="17" t="inlineStr">
-        <is>
-          <t>顧客032</t>
-        </is>
-      </c>
-      <c r="C138" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D138" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>C033</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>顧客033</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="17" t="inlineStr">
-        <is>
-          <t>C034</t>
-        </is>
-      </c>
-      <c r="B140" s="17" t="inlineStr">
-        <is>
-          <t>顧客034</t>
-        </is>
-      </c>
-      <c r="C140" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D140" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>C035</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>顧客035</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="17" t="inlineStr">
-        <is>
-          <t>C036</t>
-        </is>
-      </c>
-      <c r="B142" s="17" t="inlineStr">
-        <is>
-          <t>顧客036</t>
-        </is>
-      </c>
-      <c r="C142" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D142" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>C037</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>顧客037</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="17" t="inlineStr">
-        <is>
-          <t>C038</t>
-        </is>
-      </c>
-      <c r="B144" s="17" t="inlineStr">
-        <is>
-          <t>顧客038</t>
-        </is>
-      </c>
-      <c r="C144" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D144" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>C039</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>顧客039</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="17" t="inlineStr">
-        <is>
-          <t>C040</t>
-        </is>
-      </c>
-      <c r="B146" s="17" t="inlineStr">
-        <is>
-          <t>顧客040</t>
-        </is>
-      </c>
-      <c r="C146" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D146" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>C041</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>顧客041</t>
-        </is>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="17" t="inlineStr">
-        <is>
-          <t>C042</t>
-        </is>
-      </c>
-      <c r="B148" s="17" t="inlineStr">
-        <is>
-          <t>顧客042</t>
-        </is>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D148" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>C043</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>顧客043</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="17" t="inlineStr">
-        <is>
-          <t>C044</t>
-        </is>
-      </c>
-      <c r="B150" s="17" t="inlineStr">
-        <is>
-          <t>顧客044</t>
-        </is>
-      </c>
-      <c r="C150" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D150" s="17" t="inlineStr">
-        <is>
-          <t>ゴールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>C045</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
-        <is>
-          <t>顧客045</t>
-        </is>
-      </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>シルバー</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="17" t="inlineStr">
-        <is>
-          <t>C046</t>
-        </is>
-      </c>
-      <c r="B152" s="17" t="inlineStr">
-        <is>
-          <t>顧客046</t>
-        </is>
-      </c>
-      <c r="C152" s="17" t="inlineStr">
-        <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="D152" s="17" t="inlineStr">
-        <is>
-          <t>ブロンズ</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>C047</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
-        <is>
-          <t>顧客047</t>
-        </is>
-      </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
-        <is>
-          <t>一般</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="17" t="inlineStr">
-        <is>
-          <t>C048</t>
-        </is>
-      </c>
-      <c r="B154" s="17" t="inlineStr">
-        <is>
-          <t>顧客048</t>
-        </is>
-      </c>
-      <c r="C154" s="17" t="inlineStr">
-        <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="D154" s="17" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>ゴールド</t>
         </is>
@@ -3823,9 +2623,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
